--- a/input/reg_labourCovid19.xlsx
+++ b/input/reg_labourCovid19.xlsx
@@ -1,45 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\labsim\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0707AEC6-70E3-4670-8619-55451608B947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEC9E1D-F607-BC41-B048-3EB39F3A7F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="919" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17820" tabRatio="919" firstSheet="16" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="UK_C19LS_SE" sheetId="2" r:id="rId2"/>
-    <sheet name="UK_C19LS_E1_NE" sheetId="3" r:id="rId3"/>
-    <sheet name="UK_C19LS_E1_SE" sheetId="4" r:id="rId4"/>
-    <sheet name="UK_C19LS_E1_FF" sheetId="5" r:id="rId5"/>
-    <sheet name="UK_C19LS_E1_FX" sheetId="20" r:id="rId6"/>
-    <sheet name="UK_C19LS_E1_SC" sheetId="6" r:id="rId7"/>
-    <sheet name="UK_C19LS_E2a" sheetId="7" r:id="rId8"/>
-    <sheet name="UK_C19LS_E2b" sheetId="19" r:id="rId9"/>
-    <sheet name="UK_C19LS_FF1_E" sheetId="8" r:id="rId10"/>
-    <sheet name="UK_C19LS_FF1_FX" sheetId="21" r:id="rId11"/>
-    <sheet name="UK_C19LS_FF1_SE" sheetId="9" r:id="rId12"/>
-    <sheet name="UK_C19LS_FF1_NE" sheetId="10" r:id="rId13"/>
-    <sheet name="UK_C19LS_FX1_E" sheetId="22" r:id="rId14"/>
-    <sheet name="UK_C19LS_FX1_FF" sheetId="23" r:id="rId15"/>
-    <sheet name="UK_C19LS_FX1_SE" sheetId="24" r:id="rId16"/>
-    <sheet name="UK_C19LS_FX1_NE" sheetId="25" r:id="rId17"/>
-    <sheet name="UK_C19LS_F2a" sheetId="15" r:id="rId18"/>
-    <sheet name="UK_C19LS_F2b" sheetId="26" r:id="rId19"/>
-    <sheet name="UK_C19LS_F2c" sheetId="27" r:id="rId20"/>
-    <sheet name="UK_C19LS_S1_E" sheetId="11" r:id="rId21"/>
-    <sheet name="UK_C19LS_S1_NE" sheetId="12" r:id="rId22"/>
-    <sheet name="UK_C19LS_S2a" sheetId="16" r:id="rId23"/>
-    <sheet name="UK_C19LS_S3" sheetId="18" r:id="rId24"/>
-    <sheet name="UK_C19LS_U1_E" sheetId="13" r:id="rId25"/>
-    <sheet name="UK_C19LS_U1_SE" sheetId="14" r:id="rId26"/>
-    <sheet name="UK_C19LS_U2a" sheetId="17" r:id="rId27"/>
+    <sheet name="C19LS_SE" sheetId="2" r:id="rId2"/>
+    <sheet name="C19LS_E1_NE" sheetId="3" r:id="rId3"/>
+    <sheet name="C19LS_E1_SE" sheetId="4" r:id="rId4"/>
+    <sheet name="C19LS_E1_FF" sheetId="5" r:id="rId5"/>
+    <sheet name="C19LS_E1_FX" sheetId="20" r:id="rId6"/>
+    <sheet name="C19LS_E1_SC" sheetId="6" r:id="rId7"/>
+    <sheet name="C19LS_E2a" sheetId="7" r:id="rId8"/>
+    <sheet name="C19LS_E2b" sheetId="19" r:id="rId9"/>
+    <sheet name="C19LS_FF1_E" sheetId="8" r:id="rId10"/>
+    <sheet name="C19LS_FF1_FX" sheetId="21" r:id="rId11"/>
+    <sheet name="C19LS_FF1_SE" sheetId="9" r:id="rId12"/>
+    <sheet name="C19LS_FF1_NE" sheetId="10" r:id="rId13"/>
+    <sheet name="C19LS_FX1_E" sheetId="22" r:id="rId14"/>
+    <sheet name="C19LS_FX1_FF" sheetId="23" r:id="rId15"/>
+    <sheet name="C19LS_FX1_SE" sheetId="24" r:id="rId16"/>
+    <sheet name="C19LS_FX1_NE" sheetId="25" r:id="rId17"/>
+    <sheet name="C19LS_F2a" sheetId="15" r:id="rId18"/>
+    <sheet name="C19LS_F2b" sheetId="26" r:id="rId19"/>
+    <sheet name="C19LS_F2c" sheetId="27" r:id="rId20"/>
+    <sheet name="C19LS_S1_E" sheetId="11" r:id="rId21"/>
+    <sheet name="C19LS_S1_NE" sheetId="12" r:id="rId22"/>
+    <sheet name="C19LS_S2a" sheetId="16" r:id="rId23"/>
+    <sheet name="C19LS_S3" sheetId="18" r:id="rId24"/>
+    <sheet name="C19LS_U1_E" sheetId="13" r:id="rId25"/>
+    <sheet name="C19LS_U1_SE" sheetId="14" r:id="rId26"/>
+    <sheet name="C19LS_U2a" sheetId="17" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -192,7 +192,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +203,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -521,12 +522,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +538,7 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -547,7 +548,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -555,7 +556,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -563,7 +564,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -571,7 +572,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -579,7 +580,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -587,7 +588,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -595,7 +596,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -603,7 +604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -611,7 +612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -619,7 +620,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -627,7 +628,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -635,7 +636,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -643,7 +644,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -651,17 +652,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -678,9 +679,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E43C0E3-A7CD-477D-84A7-C1E63F25CBE2}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -688,7 +689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -696,7 +697,7 @@
         <v>0.65571920881911827</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -704,7 +705,7 @@
         <v>1.8496691805973185E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -712,7 +713,7 @@
         <v>-1.2455547463640337E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -720,7 +721,7 @@
         <v>-9.6588440837141257E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -728,7 +729,7 @@
         <v>0.1406746398450005</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -736,7 +737,7 @@
         <v>-4.4345845011429914E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -744,7 +745,7 @@
         <v>-3.9014715595468361E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -752,7 +753,7 @@
         <v>3.6392982934395746E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -760,7 +761,7 @@
         <v>-3.4367243134602676E-7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -768,7 +769,7 @@
         <v>-4.048881545523587E-7</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -784,9 +785,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE11F19F-A9E4-44C7-B034-8E3EF66B5AF6}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -794,7 +795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -802,7 +803,7 @@
         <v>3.5915890328801548E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -810,7 +811,7 @@
         <v>-2.2753702353238486E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -818,7 +819,7 @@
         <v>4.9926854289084645E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -826,7 +827,7 @@
         <v>-7.2688854748412288E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -834,7 +835,7 @@
         <v>0.25814641492274437</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -842,7 +843,7 @@
         <v>-0.75473201544058022</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -850,7 +851,7 @@
         <v>2.9155862893414999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -858,7 +859,7 @@
         <v>-5.1053843999198129E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -866,7 +867,7 @@
         <v>-8.3845005398368528E-7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -874,7 +875,7 @@
         <v>-3.2164958665368415E-6</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -890,9 +891,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51993435-9EB0-4E75-818B-F356ECA2852C}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -900,7 +901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -908,7 +909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -916,7 +917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -924,7 +925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -932,7 +933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -940,7 +941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -948,7 +949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -956,7 +957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -964,7 +965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -972,7 +973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -980,7 +981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -996,9 +997,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD240B1-501E-41EC-A1CE-707DDA5D6E04}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1006,7 +1007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1014,7 +1015,7 @@
         <v>-0.45830146502231939</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1022,7 +1023,7 @@
         <v>-1.4388259836296644E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1030,7 +1031,7 @@
         <v>1.6216009197084189E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1038,7 +1039,7 @@
         <v>-0.39646978570039892</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1046,7 +1047,7 @@
         <v>-0.12686382333833118</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1054,7 +1055,7 @@
         <v>-1.9779388221821619</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1062,7 +1063,7 @@
         <v>-0.8293989924782933</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1070,7 +1071,7 @@
         <v>-1.365553509032871</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -1078,7 +1079,7 @@
         <v>-7.3611207344581567E-7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -1086,7 +1087,7 @@
         <v>-1.4449807912347482E-6</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1102,9 +1103,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D6369A4-FC73-4D97-B33A-77AE424D5EDD}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1112,7 +1113,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1120,7 +1121,7 @@
         <v>0.29016221698066252</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1128,7 +1129,7 @@
         <v>5.0394923344151072E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1136,7 +1137,7 @@
         <v>-1.3953062082880734E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1144,7 +1145,7 @@
         <v>-6.5576351211811656E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1152,7 +1153,7 @@
         <v>7.0066869793385847E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1160,7 +1161,7 @@
         <v>0.48228785818491454</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1168,7 +1169,7 @@
         <v>0.25837425449623774</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1176,7 +1177,7 @@
         <v>0.3464337984576864</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -1184,7 +1185,7 @@
         <v>-2.3713061050589565E-9</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -1192,7 +1193,7 @@
         <v>-2.5831932648515385E-6</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1208,9 +1209,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9CC2C62-B4D4-4B72-BEC0-7EC7172397DC}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1218,7 +1219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1226,7 +1227,7 @@
         <v>-0.84442923466566677</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1234,7 +1235,7 @@
         <v>1.5975411857365188E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1242,7 +1243,7 @@
         <v>3.7742578791649629E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1250,7 +1251,7 @@
         <v>3.130875761925981E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1258,7 +1259,7 @@
         <v>0.24516890000469213</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1266,7 +1267,7 @@
         <v>1.1919615297540462</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1274,7 +1275,7 @@
         <v>0.76061116744624591</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1282,7 +1283,7 @@
         <v>0.77009072485133512</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -1290,7 +1291,7 @@
         <v>4.4447121324493764E-7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -1298,7 +1299,7 @@
         <v>4.8582093572173108E-6</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1314,9 +1315,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56DF4258-3BD5-41DA-BAF9-850CEAB1C0DB}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1324,7 +1325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1332,7 +1333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1340,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1348,7 +1349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1356,7 +1357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1364,7 +1365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1372,7 +1373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1380,7 +1381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1388,7 +1389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -1396,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -1404,7 +1405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1420,9 +1421,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C432CE5-DFD1-4A1C-8638-E7444DEA72B6}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1430,7 +1431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1438,7 +1439,7 @@
         <v>0.20428182963968938</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1446,7 +1447,7 @@
         <v>-1.0343208329843442E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1454,7 +1455,7 @@
         <v>-9.4498031729856151E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1462,7 +1463,7 @@
         <v>-0.33826455767428226</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1470,7 +1471,7 @@
         <v>-0.28456977728635802</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1478,7 +1479,7 @@
         <v>0.58243854273796436</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1486,7 +1487,7 @@
         <v>-0.26857001027155419</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1494,7 +1495,7 @@
         <v>-0.63725492459152255</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -1502,7 +1503,7 @@
         <v>-6.51418728467152E-7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -1510,7 +1511,7 @@
         <v>3.3464474964234057E-6</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1526,9 +1527,9 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AD0AEC-3C27-4329-ABA0-EC5AA135D3C8}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1536,7 +1537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1544,7 +1545,7 @@
         <v>6.7709892300710853E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1552,7 +1553,7 @@
         <v>-6.923828678764365E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1561,7 @@
         <v>7.4306152771506182E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1568,7 +1569,7 @@
         <v>-0.19578054880228074</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1576,7 +1577,7 @@
         <v>-0.179878287461568</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1584,7 +1585,7 @@
         <v>-0.23918504979782668</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1592,7 +1593,7 @@
         <v>6.2816663972150064E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1600,7 +1601,7 @@
         <v>0.18019314037568671</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1608,7 +1609,7 @@
         <v>2.0683259521419349E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1624,9 +1625,9 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F45AEC-943B-4AA7-A859-68375F8A05AC}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1634,7 +1635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1642,7 +1643,7 @@
         <v>2.3364340034587153E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1650,7 +1651,7 @@
         <v>-9.746038443592937E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1658,7 +1659,7 @@
         <v>8.0344793967495314E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1666,7 +1667,7 @@
         <v>6.6028525697884796E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1674,7 +1675,7 @@
         <v>-3.6880920962927437E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1682,7 +1683,7 @@
         <v>-0.16412973734100716</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1690,7 +1691,7 @@
         <v>0.12644842623759103</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1698,7 +1699,7 @@
         <v>0.11192288122494244</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1706,7 +1707,7 @@
         <v>-4.3283375183295787E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1722,9 +1723,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C98ADB-6040-40BA-AC83-95A5AE470D49}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1732,7 +1733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1740,7 +1741,7 @@
         <v>3.9344999999999996E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1748,7 +1749,7 @@
         <v>6.2175800000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1764,9 +1765,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A1751D-AE31-403F-BF64-495AC3206CD2}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1774,7 +1775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1782,7 +1783,7 @@
         <v>6.7709892300710853E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1790,7 +1791,7 @@
         <v>-6.923828678764365E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1798,7 +1799,7 @@
         <v>7.4306152771506182E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1806,7 +1807,7 @@
         <v>-0.19578054880228074</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1814,7 +1815,7 @@
         <v>-0.179878287461568</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1822,7 +1823,7 @@
         <v>-0.23918504979782668</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1830,7 +1831,7 @@
         <v>6.2816663972150064E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1838,7 +1839,7 @@
         <v>0.18019314037568671</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1846,7 +1847,7 @@
         <v>2.0683259521419349E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1862,9 +1863,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E9197C1-1710-4E3B-9EE3-FEBE1DCC07A4}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1872,7 +1873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1880,7 +1881,7 @@
         <v>-5.5608946527180493E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1888,7 +1889,7 @@
         <v>-3.2616983619096221E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1896,7 +1897,7 @@
         <v>4.0002541910364921E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1904,7 +1905,7 @@
         <v>-0.2497614879308796</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1912,7 +1913,7 @@
         <v>-0.24185791678577023</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1920,7 +1921,7 @@
         <v>-0.40472922946325846</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1928,7 +1929,7 @@
         <v>-0.4487324199792998</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1936,7 +1937,7 @@
         <v>-0.43074702507987378</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1952,9 +1953,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE6D2A10-E57E-42B0-AFE1-D0E92133582D}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1962,7 +1963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1970,7 +1971,7 @@
         <v>1.2035752913303042</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1978,7 +1979,7 @@
         <v>-7.3835261372464942E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1986,7 +1987,7 @@
         <v>-3.0853449047844244E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1994,7 +1995,7 @@
         <v>8.509481177837018E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2002,7 +2003,7 @@
         <v>9.8707238399044842E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2010,7 +2011,7 @@
         <v>-0.28937527649784939</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2018,7 +2019,7 @@
         <v>-0.30393107375517292</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2026,7 +2027,7 @@
         <v>-0.38309407455942973</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -2042,9 +2043,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A93F1A09-0280-4DDA-95D8-F4D0197C2120}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2052,7 +2053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2060,7 +2061,7 @@
         <v>0.66338983295548259</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2068,7 +2069,7 @@
         <v>-6.19607613815004E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2076,7 +2077,7 @@
         <v>-4.3258253654007151E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -2084,7 +2085,7 @@
         <v>0.30000321467635033</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -2092,7 +2093,7 @@
         <v>-0.14075553242308506</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -2100,7 +2101,7 @@
         <v>-9.9444264284179167E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2108,7 +2109,7 @@
         <v>-0.10068382759674693</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2116,7 +2117,7 @@
         <v>3.038793395674427E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -2124,7 +2125,7 @@
         <v>4.1973336474744272E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -2140,9 +2141,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D5D2D7D-48E1-4050-82AD-7BCC833FC315}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2150,7 +2151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2158,7 +2159,7 @@
         <v>-0.50637575966566906</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2166,7 +2167,7 @@
         <v>-1.8821356317172661E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2174,7 +2175,7 @@
         <v>9.4696178037368579E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2182,7 +2183,7 @@
         <v>-0.1626966439145853</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2190,7 +2191,7 @@
         <v>0.18243848475643526</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2198,7 +2199,7 @@
         <v>-0.20523796757437748</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2206,7 +2207,7 @@
         <v>-0.39605635967831254</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2214,7 +2215,7 @@
         <v>-0.30888609043623599</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -2222,7 +2223,7 @@
         <v>3.7640678887172767E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -2230,7 +2231,7 @@
         <v>-1.2731186231064361E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -2238,7 +2239,7 @@
         <v>0.70244518046650561</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -2246,7 +2247,7 @@
         <v>1.0273147300287071</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -2254,7 +2255,7 @@
         <v>1.13447937770045</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -2262,7 +2263,7 @@
         <v>0.60484720632431999</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -2270,7 +2271,7 @@
         <v>-2.2347098321189973E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2278,7 +2279,7 @@
         <v>6.4756645974800771</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -2286,7 +2287,7 @@
         <v>-0.87854060597180506</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -2302,9 +2303,9 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51939863-E45E-4002-8EDF-890720B8AEE5}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2312,7 +2313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2320,7 +2321,7 @@
         <v>0.27218129358505611</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2328,7 +2329,7 @@
         <v>-4.5561339731719441E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2336,7 +2337,7 @@
         <v>-2.275398124776722E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2344,7 +2345,7 @@
         <v>-0.49968032576526006</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2352,7 +2353,7 @@
         <v>-0.91464774085903877</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2360,7 +2361,7 @@
         <v>-0.14350278146617365</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2368,7 +2369,7 @@
         <v>-7.7549901082278092E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2376,7 +2377,7 @@
         <v>5.8471232434248184E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -2384,7 +2385,7 @@
         <v>1.678188833037777</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -2400,9 +2401,9 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40D5AE9-27DB-4BE2-9D33-778F5CAF7848}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2410,7 +2411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2418,7 +2419,7 @@
         <v>1.2750640582405603</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2426,7 +2427,7 @@
         <v>1.6206742382189425E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2434,7 +2435,7 @@
         <v>-1.8575045696497709E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2442,7 +2443,7 @@
         <v>-0.41014255284949214</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2450,7 +2451,7 @@
         <v>-0.99589911140740195</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2458,7 +2459,7 @@
         <v>-0.33101307599842739</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2466,7 +2467,7 @@
         <v>-0.10944254471789193</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2474,7 +2475,7 @@
         <v>0.33015739987419418</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -2482,7 +2483,7 @@
         <v>0.81694280151181464</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -2498,9 +2499,9 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7BFC270-1BDA-4735-BB50-ADC3E0E21A5C}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2508,7 +2509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2516,7 +2517,7 @@
         <v>-5.728567317427543E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2524,7 +2525,7 @@
         <v>-7.3919931984700368E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2532,7 +2533,7 @@
         <v>8.663182191850239E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -2540,7 +2541,7 @@
         <v>-0.43132820692660956</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -2548,7 +2549,7 @@
         <v>3.4391061138786781E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -2556,7 +2557,7 @@
         <v>3.0902610061017749E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2564,7 +2565,7 @@
         <v>-7.8664907218404023E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2572,7 +2573,7 @@
         <v>4.960323805922244E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -2580,7 +2581,7 @@
         <v>2.0454132517669494E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -2596,12 +2597,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3684C8C-B1C8-4AD0-A4D4-558FBE5D65E1}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2609,7 +2610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2617,7 +2618,7 @@
         <v>-0.81646173587379656</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2625,7 +2626,7 @@
         <v>-2.456027671535992E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2633,7 +2634,7 @@
         <v>1.5734480899413563E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2641,7 +2642,7 @@
         <v>0.48764465156251841</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2649,7 +2650,7 @@
         <v>0.94309280635100434</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2657,7 +2658,7 @@
         <v>7.0496977947678728E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2665,7 +2666,7 @@
         <v>0.25959961589448388</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2673,7 +2674,7 @@
         <v>-0.25097012670845742</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -2681,7 +2682,7 @@
         <v>-6.062554224318473E-8</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -2689,7 +2690,7 @@
         <v>-5.1415048423764064E-7</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -2705,9 +2706,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D77E2E6F-4D47-4794-BD13-169D62BD2424}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2715,7 +2716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2723,7 +2724,7 @@
         <v>-0.61441880999846032</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2731,7 +2732,7 @@
         <v>2.6947673766859566E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2739,7 +2740,7 @@
         <v>2.3109249735112008E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2747,7 +2748,7 @@
         <v>0.30996212534983814</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2755,7 +2756,7 @@
         <v>0.75973072076889436</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2763,7 +2764,7 @@
         <v>8.68590086497108E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2771,7 +2772,7 @@
         <v>-0.14694997397093915</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2779,7 +2780,7 @@
         <v>0.22625613392743685</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -2787,7 +2788,7 @@
         <v>-7.9562248242776506E-7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -2795,7 +2796,7 @@
         <v>-3.6698368615425799E-6</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -2811,9 +2812,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC566532-EBF3-4998-BF75-4E19C0A184D0}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2821,7 +2822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2829,7 +2830,7 @@
         <v>-0.33710740603648948</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2837,7 +2838,7 @@
         <v>-2.0338473046677911E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2845,7 +2846,7 @@
         <v>9.9550128213089437E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2853,7 +2854,7 @@
         <v>0.92048502013058975</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2861,7 +2862,7 @@
         <v>1.3514285579776415</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2869,7 +2870,7 @@
         <v>0.13365264087323056</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2877,7 +2878,7 @@
         <v>0.24101568365619777</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2885,7 +2886,7 @@
         <v>-2.2828962676823387E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -2893,7 +2894,7 @@
         <v>1.0068722210117578E-6</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -2901,7 +2902,7 @@
         <v>2.8769757650003242E-6</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -2917,9 +2918,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D546180A-DBEA-4336-9B1E-2C3E6208FC8D}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2927,7 +2928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2935,7 +2936,7 @@
         <v>-0.82390205924971915</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2943,7 +2944,7 @@
         <v>-2.61388553848809E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2951,7 +2952,7 @@
         <v>2.6616902473235719E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2959,7 +2960,7 @@
         <v>0.69384646055087351</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2967,7 +2968,7 @@
         <v>1.2912138965011519</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2975,7 +2976,7 @@
         <v>-0.5085053248595881</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2983,7 +2984,7 @@
         <v>4.6200273469234672E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2991,7 +2992,7 @@
         <v>-0.29031216083234879</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -2999,7 +3000,7 @@
         <v>-1.9876371851049397E-7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -3007,7 +3008,7 @@
         <v>6.2621596686698093E-7</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -3023,12 +3024,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE15CC9D-6659-4D74-B182-A651119EC6AB}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -3036,7 +3037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3044,7 +3045,7 @@
         <v>-0.28530713533838736</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -3052,7 +3053,7 @@
         <v>-1.0372899901898321E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3060,7 +3061,7 @@
         <v>6.4333316003632388E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3068,7 +3069,7 @@
         <v>0.10076139328053969</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -3076,7 +3077,7 @@
         <v>-4.1554047523925846E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -3084,7 +3085,7 @@
         <v>-2.7346048270541014E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -3092,7 +3093,7 @@
         <v>1.6100103385781959E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -3100,7 +3101,7 @@
         <v>-3.6100644817824083E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -3108,7 +3109,7 @@
         <v>-6.2541530581314193E-8</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -3116,7 +3117,7 @@
         <v>-1.1802003914003328E-7</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -3132,9 +3133,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F56D19-93E5-4385-8533-42A5E95F1391}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -3142,7 +3143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3150,7 +3151,7 @@
         <v>0.21080155081965293</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -3158,7 +3159,7 @@
         <v>-2.8778702904321148E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3166,7 +3167,7 @@
         <v>4.5854659172632348E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -3174,7 +3175,7 @@
         <v>-0.13175820256500603</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -3182,7 +3183,7 @@
         <v>-5.3517664634090287E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -3190,7 +3191,7 @@
         <v>-0.10321481303132186</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3198,7 +3199,7 @@
         <v>-6.3559073163286156E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -3206,7 +3207,7 @@
         <v>-7.6910978191564172E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -3214,7 +3215,7 @@
         <v>1.7753654003716431E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -3231,9 +3232,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F11B5EB-7D89-4106-A878-39AB04F189DD}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -3241,7 +3242,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3249,7 +3250,7 @@
         <v>-9.9409946244495381E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -3257,7 +3258,7 @@
         <v>-9.5225302481199616E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3265,7 +3266,7 @@
         <v>9.5734879085979524E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -3273,7 +3274,7 @@
         <v>-0.12360967909380145</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -3281,7 +3282,7 @@
         <v>-0.12528805175495433</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -3289,7 +3290,7 @@
         <v>-0.2254191061739288</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3297,7 +3298,7 @@
         <v>7.0277970468888409E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -3305,7 +3306,7 @@
         <v>0.17830133902802775</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -3313,7 +3314,7 @@
         <v>-7.1663339835166574E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
